--- a/astro-site/public/dl/coffee-shop-checklist-templates/05-cafe-cleaning-checklist-inventory-maintenance.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/05-cafe-cleaning-checklist-inventory-maintenance.xlsx
@@ -350,11 +350,11 @@
     <xf numFmtId="4" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -838,10 +838,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
+    <row r="23" ht="47" customHeight="1">
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>▸ Sheets with formulas are protected WITHOUT a password: the input cells (the green ones) are unlocked, so calculations never get overwritten by accident.</t>
+          <t>▸ Checklist sheets with formulas are protected WITHOUT a password: the input cells (the green ones) are unlocked. The two inventory sheets are left unprotected so you can add products: don't type over the Status or Total value columns.</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Whole milk</t>
+          <t>Whole milk (1 gal = 4 qt)</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -1548,11 +1548,11 @@
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>lb</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E34" s="9">
         <f>IF(B34="","",IF(B34&lt;D34,"⚠️ REORDER","OK"))</f>
@@ -1870,7 +1870,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>House blend coffee (2 lb bags)</t>
+          <t>House blend coffee (5 lb or 2 lb bags)</t>
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
@@ -1972,7 +1972,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Whole milk (cartons/bottles)</t>
+          <t>Whole milk (1 gal = 4 qt)</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -2884,9 +2884,9 @@
       <c r="A7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>Take apart and clean the exhaust hood</t>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>Remove and degrease the hood filters (hood and duct cleaning is the contractor's job: see Quarterly &amp; Annual)</t>
         </is>
       </c>
       <c r="C7" s="38" t="inlineStr">
@@ -3059,7 +3059,7 @@
       <c r="A14" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>Clean the espresso group heads with the group brush</t>
         </is>
@@ -3113,9 +3113,9 @@
       <c r="A16" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>Clean inside the bar fridge</t>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>Clean inside the bar fridge; check the ice machine bin and chute for mold or slime (full clean and sanitize per the manufacturer)</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B9" s="41" t="inlineStr">
         <is>
-          <t>Check the temperatures of all walk-ins (cooler 41 °F or below, freezer 0 °F or below) — log reading: ____ °F</t>
+          <t>Check the temperatures of all coolers and freezers (cooler 41 °F or below, freezer 0 °F or below) — log reading: cooler ____ °F · freezer ____ °F</t>
         </is>
       </c>
       <c r="C9" s="38" t="inlineStr">
@@ -3660,9 +3660,9 @@
       <c r="A11" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>Check expiration dates on opened milk: the manufacturer's label date and the date you wrote when you opened it rule; keep it at 41 °F or below</t>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>Check dates on opened milk: toss it at 7 days counting the day it was opened or at the label's use-by date, whichever comes first; keep it at 41 °F or below</t>
         </is>
       </c>
       <c r="C11" s="38" t="inlineStr">
@@ -4387,7 +4387,7 @@
       <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Descale the whole espresso machine per the manufacturer's instructions</t>
         </is>
@@ -4468,9 +4468,9 @@
       <c r="A9" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="41" t="inlineStr">
-        <is>
-          <t>Clean the water filter</t>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>Check the water filter: pressure/flow and capacity used (change it on the Quarterly &amp; Annual schedule)</t>
         </is>
       </c>
       <c r="C9" s="38" t="inlineStr">
